--- a/SCE_mean.xlsx
+++ b/SCE_mean.xlsx
@@ -69,7 +69,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,7 +420,7 @@
         <v>42248</v>
       </c>
       <c r="B34" s="2">
-        <v>5.8450186539383751</v>
+        <v>5.8450186539383742</v>
       </c>
       <c r="C34" s="2">
         <v>3</v>
@@ -563,7 +563,7 @@
         <v>42644</v>
       </c>
       <c r="B47" s="2">
-        <v>5.6762091874374212</v>
+        <v>5.6762091874374203</v>
       </c>
       <c r="C47" s="2">
         <v>3</v>
@@ -596,7 +596,7 @@
         <v>42736</v>
       </c>
       <c r="B50" s="2">
-        <v>3.5363224359186951</v>
+        <v>3.5363224359187027</v>
       </c>
       <c r="C50" s="2">
         <v>3</v>
@@ -739,7 +739,7 @@
         <v>43132</v>
       </c>
       <c r="B63" s="2">
-        <v>4.3152441953006555</v>
+        <v>4.3152441953006493</v>
       </c>
       <c r="C63" s="2">
         <v>3</v>
@@ -882,7 +882,7 @@
         <v>43525</v>
       </c>
       <c r="B76" s="2">
-        <v>5.4014098567685425</v>
+        <v>5.4014098567685433</v>
       </c>
       <c r="C76" s="2">
         <v>3.5499999523162842</v>
@@ -1355,7 +1355,7 @@
         <v>44835</v>
       </c>
       <c r="B119" s="2">
-        <v>8.1706940260646324</v>
+        <v>8.1706940260646341</v>
       </c>
       <c r="C119" s="2">
         <v>7</v>
@@ -1377,7 +1377,7 @@
         <v>44896</v>
       </c>
       <c r="B121" s="2">
-        <v>6.6232865476542875</v>
+        <v>6.6232865476542866</v>
       </c>
       <c r="C121" s="2">
         <v>6</v>
@@ -1596,64 +1596,156 @@
       <c r="A141" s="1">
         <v>45505</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
+      <c r="B141" s="2">
+        <v>1.4425706169935895</v>
+      </c>
+      <c r="C141" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
+      <c r="B142" s="2">
+        <v>3.6871927207885218</v>
+      </c>
+      <c r="C142" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
+      <c r="B143" s="2">
+        <v>3.1735335656495645</v>
+      </c>
+      <c r="C143" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
+      <c r="B144" s="2">
+        <v>2.3419419048992816</v>
+      </c>
+      <c r="C144" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
+      <c r="B145" s="2">
+        <v>2.7375487698700143</v>
+      </c>
+      <c r="C145" s="2">
+        <v>3.1500000953674316</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
+      <c r="B146" s="2">
+        <v>0.42355947682782152</v>
+      </c>
+      <c r="C146" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
+      <c r="B147" s="2">
+        <v>4.540698861737785</v>
+      </c>
+      <c r="C147" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
+      <c r="B148" s="2">
+        <v>4.0448347214114442</v>
+      </c>
+      <c r="C148" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
+      <c r="B149" s="2">
+        <v>3.3950718471462022</v>
+      </c>
+      <c r="C149" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
     </row>
   </sheetData>
 </worksheet>
